--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:35:38+00:00</t>
+    <t>2024-04-08T14:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,9 +323,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:type</t>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:type.value[x]</t>
@@ -1322,24 +1322,24 @@
         <v>80</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>78</v>
@@ -1364,10 +1364,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1427,7 +1427,7 @@
         <v>80</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1573,7 +1573,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1633,7 +1633,7 @@
         <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1670,16 +1670,16 @@
         <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>78</v>
@@ -1729,22 +1729,22 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1839,13 +1839,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -1884,7 +1884,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1944,7 +1944,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1958,7 +1958,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2061,7 +2061,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2090,7 +2090,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2150,7 +2150,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2164,7 +2164,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2187,16 +2187,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2246,22 +2246,22 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2358,13 +2358,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -2403,7 +2403,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2463,7 +2463,7 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2477,7 +2477,7 @@
         <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2580,7 +2580,7 @@
         <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2609,7 +2609,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2669,7 +2669,7 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2683,7 +2683,7 @@
         <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2706,16 +2706,16 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2765,22 +2765,22 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2877,13 +2877,13 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -2922,7 +2922,7 @@
         <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2982,7 +2982,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>83</v>
@@ -2996,7 +2996,7 @@
         <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3099,7 +3099,7 @@
         <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3128,7 +3128,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3188,7 +3188,7 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>83</v>
@@ -3202,7 +3202,7 @@
         <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3225,16 +3225,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3284,22 +3284,22 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -3396,13 +3396,13 @@
         <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -3441,7 +3441,7 @@
         <v>149</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3501,7 +3501,7 @@
         <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>83</v>
@@ -3515,7 +3515,7 @@
         <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3618,7 +3618,7 @@
         <v>151</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3647,7 +3647,7 @@
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3707,7 +3707,7 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>83</v>
@@ -3721,7 +3721,7 @@
         <v>152</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3744,16 +3744,16 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3803,22 +3803,22 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="29">
@@ -3915,13 +3915,13 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30">
@@ -3960,7 +3960,7 @@
         <v>156</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4020,7 +4020,7 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>83</v>
@@ -4034,7 +4034,7 @@
         <v>157</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4137,7 +4137,7 @@
         <v>158</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4166,7 +4166,7 @@
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4226,7 +4226,7 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>83</v>
@@ -4240,7 +4240,7 @@
         <v>159</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4263,16 +4263,16 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4322,22 +4322,22 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="34">
@@ -4434,13 +4434,13 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
@@ -4479,7 +4479,7 @@
         <v>164</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4539,7 +4539,7 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>83</v>
@@ -4553,7 +4553,7 @@
         <v>165</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4656,7 +4656,7 @@
         <v>166</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4685,7 +4685,7 @@
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4745,7 +4745,7 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>83</v>
@@ -4759,7 +4759,7 @@
         <v>167</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4782,16 +4782,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4841,22 +4841,22 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="39">
@@ -4953,21 +4953,21 @@
         <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4990,16 +4990,16 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5049,22 +5049,22 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="41">
@@ -5161,13 +5161,13 @@
         <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
